--- a/病案数据调取_填报模板_v1.xlsx
+++ b/病案数据调取_填报模板_v1.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3项_消化道异物住院人次" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第4项_病区沿革确认" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第5项_全院住院总人次" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第6项_穿孔相关编码住院人次" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -713,69 +714,81 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>第6项（必需）</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>穿孔相关诊断编码组逐月住院人次（全院）——用于核对本课题病例检索是否完整</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>三、重要提示</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>病区更名</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>据了解，2024 年 8 月前后普外一病区更名为胃肠外科病区、普外二病区更名为肝胆外科/肿瘤外科病区，在此之前该两病区并未设立。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>更名前后的四个名称在模板中均已单独列出，请按各年月实际情况分别填写，不要预先合并。本课题将在分析时自行归并，因此某名称在某些年份无数据时请填 0——这一信息对我们同样重要。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>名称变体</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>若贵室系统中另有「胃肠外科」「肝胆外科/肿瘤外科」等不带「病区」二字的写法，请一并计入对应列。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2019-07～2020-03</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>本课题的科研平台导出在这 9 个月为空。请按贵室病案首页系统的实际数字照常填报，不要填 0；若贵室系统同样缺失，请在第 4 项注明。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>保密说明</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>本次调取均为汇总计数，不含任何患者可识别信息，仅用于上述已获伦理批准课题的分母估计与发生率分析。</t>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>本次调取均为汇总计数，不含任何患者可识别信息，仅用于上述已获伦理批准课题的分母估计、发生率分析及病例检索完整性核对。</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6767,7 @@
     <row r="9" ht="78" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>4. 2019 年 7 月至 2020 年 3 月的住院数据是否完整？本课题从院内科研数据平台导出的两份数据（胃十二指肠穿孔、消化道异物）在这 9 个月内住院记录均为零，而前后月份均正常（消化道异物住院每月 5 至 15 次），推测为平台数据缺失。请说明：（1）贵室病案首页系统在此期间的住院数据是否完整；（2）若完整，第 1、2、3、5 项请照常填报这 9 个月的实际数字，不要因科研平台缺失而填 0；（3）如知晓科研平台缺失的原因（如系统切换、数据迁移）及能否补导，请一并说明。</t>
+          <t>4. 2019 年 7 月至 2020 年 3 月的住院数据是否完整？本课题从院内科研数据平台导出的两份数据（胃十二指肠穿孔、消化道异物）在这 9 个月内住院记录均为零，而前后月份均正常（消化道异物住院每月 5 至 15 次），推测为平台数据缺失。请说明：（1）贵室病案首页系统在此期间的住院数据是否完整；（2）若完整，第 1、2、3、5、6 项请照常填报这 9 个月的实际数字，不要因科研平台缺失而填 0；（3）如知晓科研平台缺失的原因（如系统切换、数据迁移）及能否补导，请一并说明。</t>
         </is>
       </c>
       <c r="B9" s="13" t="n"/>
@@ -7964,4 +7977,1841 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H130"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>第 6 项（必需）穿孔相关诊断编码组 逐月住院人次——全院，不限病区；用于核对本课题病例检索是否完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>筛选：出院诊断（主要或其他诊断任一出现）属于下列编码组；同一次住院出现多组时各组分别计入，「合计（去重）」只计 1 次。同组内含义相同的其他亚目请一并计入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>本课题病例中出现过的编码：组1 K31.814、K31.813；组2 K31.800x806；组3 K25.101、K26.100、K26.500x001、K27.501（即 K25–K27 的 .1/.2/.5/.6 伴穿孔亚目）；组4 P78.800x009、Q40.204；组5 S36.300、S36.405（S36.3 全部亚目及 S36.4 下十二指肠损伤亚目）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>组1 胃穿孔/胃破裂</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>组2 十二指肠穿孔</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>组3 消化性溃疡伴穿孔</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>组4 新生儿胃穿孔/胃壁肌层缺损</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>组5 胃/十二指肠损伤</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>合计（去重）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+      <c r="H63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="n"/>
+      <c r="H64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
+      <c r="H69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n"/>
+      <c r="H71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n"/>
+      <c r="H73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+      <c r="H75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B98" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="9" t="n"/>
+      <c r="H99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B100" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="9" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
+      <c r="H101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
+      <c r="H103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="9" t="n"/>
+      <c r="H105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B106" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="9" t="n"/>
+      <c r="H107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B108" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="9" t="n"/>
+      <c r="H108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="9" t="n"/>
+      <c r="H110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" s="9" t="n"/>
+      <c r="D111" s="9" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="9" t="n"/>
+      <c r="H111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B112" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="9" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="9" t="n"/>
+      <c r="H114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="9" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="9" t="n"/>
+      <c r="H115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B116" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
+      <c r="H116" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B117" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+      <c r="H117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B118" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
+      <c r="H118" s="9" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="9" t="n"/>
+      <c r="H119" s="9" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B120" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="9" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="9" t="n"/>
+      <c r="G120" s="9" t="n"/>
+      <c r="H120" s="9" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B121" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="9" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="9" t="n"/>
+      <c r="G121" s="9" t="n"/>
+      <c r="H121" s="9" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B122" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="9" t="n"/>
+      <c r="H122" s="9" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B123" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="9" t="n"/>
+      <c r="H123" s="9" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B124" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="9" t="n"/>
+      <c r="H124" s="9" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B125" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="9" t="n"/>
+      <c r="H125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B126" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="9" t="n"/>
+      <c r="H126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B127" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
+      <c r="H127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="9" t="n"/>
+      <c r="H128" s="9" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B129" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="9" t="n"/>
+      <c r="H129" s="9" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B130" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="9" t="n"/>
+      <c r="G130" s="9" t="n"/>
+      <c r="H130" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>